--- a/artfynd/A 56599-2024 artfynd.xlsx
+++ b/artfynd/A 56599-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557584</v>
+        <v>121557696</v>
       </c>
       <c r="B2" t="n">
-        <v>100370</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492619</v>
+        <v>492620</v>
       </c>
       <c r="R2" t="n">
-        <v>7016523</v>
+        <v>7016430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557696</v>
+        <v>121557584</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,24 +803,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492620</v>
+        <v>492619</v>
       </c>
       <c r="R3" t="n">
-        <v>7016430</v>
+        <v>7016523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>121564869</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 56599-2024 artfynd.xlsx
+++ b/artfynd/A 56599-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557696</v>
+        <v>121557584</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -720,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492620</v>
+        <v>492619</v>
       </c>
       <c r="R2" t="n">
-        <v>7016430</v>
+        <v>7016523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +774,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557584</v>
+        <v>121557696</v>
       </c>
       <c r="B3" t="n">
-        <v>100371</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,29 +808,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492619</v>
+        <v>492620</v>
       </c>
       <c r="R3" t="n">
-        <v>7016523</v>
+        <v>7016430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 56599-2024 artfynd.xlsx
+++ b/artfynd/A 56599-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557584</v>
+        <v>121557696</v>
       </c>
       <c r="B2" t="n">
-        <v>100371</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492619</v>
+        <v>492620</v>
       </c>
       <c r="R2" t="n">
-        <v>7016523</v>
+        <v>7016430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557696</v>
+        <v>121557584</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,24 +803,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492620</v>
+        <v>492619</v>
       </c>
       <c r="R3" t="n">
-        <v>7016430</v>
+        <v>7016523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 56599-2024 artfynd.xlsx
+++ b/artfynd/A 56599-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557584</v>
+        <v>121557696</v>
       </c>
       <c r="B2" t="n">
-        <v>100379</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492619</v>
+        <v>492620</v>
       </c>
       <c r="R2" t="n">
-        <v>7016523</v>
+        <v>7016430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557696</v>
+        <v>121557584</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>100379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,24 +803,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492620</v>
+        <v>492619</v>
       </c>
       <c r="R3" t="n">
-        <v>7016430</v>
+        <v>7016523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
